--- a/testfiles/import/Serial.xlsx
+++ b/testfiles/import/Serial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Engine\NimbleAnalyzer2\testfiles\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B97FEF-664C-4DD5-942B-3278AB066612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E413D5-5DA4-40FF-8BAB-E61C55199B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43950" yWindow="7905" windowWidth="28755" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41130" yWindow="3255" windowWidth="28755" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>SN</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Adrian Jahraus</t>
+  </si>
+  <si>
+    <t>Y:\Produktion\Prüffeld\Prüfprotokolle\Xe-µJoule</t>
   </si>
 </sst>
 </file>
@@ -424,7 +427,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1">
         <v>46050</v>
@@ -435,10 +438,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1">
-        <v>46050</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -446,10 +449,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1">
-        <v>46050</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -457,10 +460,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
-        <v>46050</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -468,10 +471,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>46050</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,10 +482,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>46050</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -493,7 +496,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>46050</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -504,7 +507,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="1">
-        <v>46050</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -515,7 +518,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="1">
-        <v>46050</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -526,7 +529,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="1">
-        <v>46050</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -537,7 +540,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>46050</v>
+        <v>46060</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -548,7 +551,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="1">
-        <v>46050</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -559,7 +562,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="1">
-        <v>46050</v>
+        <v>46062</v>
       </c>
     </row>
   </sheetData>
